--- a/SALT_STRATEGY_1410.xlsx
+++ b/SALT_STRATEGY_1410.xlsx
@@ -104,46 +104,54 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +515,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,648 +526,687 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Соль: себестоимость с доставкой и наша прибыль по 4 вариантам поставки (снижение 15%, чистая после УСН 15%)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Лучший реальный вариант — ближайший источник (вариант 2 или 3). Вариант 1 — ваша цена, нужно подтвердить. Все варианты кроме 1 — расчётные по открытым ценам.</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="81" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Лот</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Подача</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Тонн</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Цена в НМЦК, ₽/т</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): ₽/т</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): маржа</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): прибыль, ₽</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: ₽/т</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: маржа</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: прибыль, ₽</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>3. Ближайший склад авто: ₽/т</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>3. Ближайший склад авто: маржа</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>3. Ближайший склад авто: прибыль, ₽</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>4. Дилер с доставкой (рынок): ₽/т</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>4. Дилер с доставкой (рынок): маржа</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>4. Дилер с доставкой (рынок): прибыль, ₽</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Рекомендуемая стратегия</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Прибыль при рекомендуемой, ₽</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ДГХ, Московская обл.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>32616451106</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>16.10 10:00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>6724000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>16810</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="8" t="n">
         <v>0.851279000594884</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="9" t="n">
         <v>3941280.074520547</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <v>4770</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="8" t="n">
         <v>0.7162403331350387</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="9" t="n">
         <v>3144105.827945205</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="6" t="n">
         <v>4970</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="8" t="n">
         <v>0.7043426531826293</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="9" t="n">
         <v>3073870.211506849</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="P4" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="Q4" s="8" t="n">
         <v>0.5240928019036288</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="R4" s="9" t="n">
         <v>2009800.622465753</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 770 ₽/т</t>
         </is>
       </c>
-      <c r="T4" s="8" t="n">
+      <c r="T4" s="10" t="n">
         <v>3144105.827945205</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Новосибирск, «Дзержинка»</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0851300006226000106</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>16.10 05:00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>4400000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="8" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>2275622.794520548</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>4310</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="8" t="n">
         <v>0.6081818181818182</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" s="9" t="n">
         <v>1639990.465753425</v>
       </c>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="6" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n">
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="R5" s="9" t="n">
         <v>344143.3424657534</v>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 310 ₽/т</t>
         </is>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="10" t="n">
         <v>1639990.465753425</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Волоколамск, МО</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>32616447519</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>16.10 10:00</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>1593800</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>12260</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="8" t="n">
         <v>0.7960848287112561</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>856976.144219178</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>4650</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="8" t="n">
         <v>0.6207177814029364</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="L6" s="9" t="n">
         <v>611590.4592876713</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="M6" s="6" t="n">
         <v>5330</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="8" t="n">
         <v>0.5652528548123981</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="O6" s="9" t="n">
         <v>533980.1031232877</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="P6" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="Q6" s="8" t="n">
         <v>0.3474714518760196</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="11" t="n">
         <v>229245.3223013698</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 650 ₽/т</t>
         </is>
       </c>
-      <c r="T6" s="8" t="n">
+      <c r="T6" s="10" t="n">
         <v>611590.4592876713</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Абинск, Краснодарский край</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>0318300065126000256</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>19.10 09:00</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>1368000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>9120</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="8" t="n">
         <v>0.7258771929824561</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>651243.5079452054</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>5090</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="8" t="n">
         <v>0.4418859649122807</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="9" t="n">
         <v>310161.7956164384</v>
       </c>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n">
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q7" s="8" t="n">
         <v>0.1228070175438596</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="12" t="n">
         <v>-85954.45479452054</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 5 090 ₽/т</t>
         </is>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="T7" s="10" t="n">
         <v>310161.7956164384</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Воронеж</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>0131300000626001316</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>16.10 09:00</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>3296150</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="7" t="n">
         <v>461</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>7150</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="8" t="n">
         <v>0.6503496503496503</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>1350584.778684932</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>4650</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="8" t="n">
         <v>0.3496503496503496</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="9" t="n">
         <v>480409.3882739726</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="6" t="n">
         <v>7670</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="N8" s="8" t="n">
         <v>-0.07272727272727272</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="12" t="n">
         <v>-872804.1008219178</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="P8" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="Q8" s="8" t="n">
         <v>-0.1188811188811189</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="12" t="n">
         <v>-1029935.635068493</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 650 ₽/т</t>
         </is>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="10" t="n">
         <v>480409.3882739726</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Струнино, Владимирская обл.</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>0128600006826000407</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>19.10</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>1342500</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>8950</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="8" t="n">
         <v>0.7206703910614525</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="9" t="n">
         <v>632967.1479452054</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>4910</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="8" t="n">
         <v>0.4513966480446928</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="9" t="n">
         <v>315589.9561643836</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="6" t="n">
         <v>5210</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="8" t="n">
         <v>0.417877094972067</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" s="11" t="n">
         <v>276082.4219178082</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="P9" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q9" s="8" t="n">
         <v>0.106145251396648</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="12" t="n">
         <v>-107456.0547945205</v>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 910 ₽/т</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
+      <c r="T9" s="10" t="n">
         <v>315589.9561643836</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Самара (нужен опыт 24,2 млн)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>0142200001326018965</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>19.10 11:00</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>121000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="7" t="n">
         <v>11000</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>2500</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="8" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="9" t="n">
         <v>62579626.84931506</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>3850</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="8" t="n">
         <v>0.65</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="9" t="n">
         <v>49542140.5479452</v>
       </c>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n">
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="Q10" s="8" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="R10" s="9" t="n">
         <v>9463941.91780822</v>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 3 850 ₽/т</t>
         </is>
       </c>
-      <c r="T10" s="8" t="n">
+      <c r="T10" s="10" t="n">
         <v>49542140.5479452</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>ИТОГО без Самары</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr"/>
-      <c r="C11" s="11" t="inlineStr"/>
-      <c r="D11" s="11" t="inlineStr"/>
-      <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr"/>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="8" t="n">
+      <c r="B11" s="13" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="10" t="n">
         <v>9708674.447835615</v>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr"/>
-      <c r="L11" s="8" t="n">
+      <c r="J11" s="13" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="10" t="n">
         <v>6501847.893041097</v>
       </c>
-      <c r="M11" s="11" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="8" t="n">
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr"/>
+      <c r="O11" s="10" t="n">
         <v>3011128.635726027</v>
       </c>
-      <c r="P11" s="11" t="inlineStr"/>
-      <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="8" t="n">
+      <c r="P11" s="13" t="inlineStr"/>
+      <c r="Q11" s="13" t="inlineStr"/>
+      <c r="R11" s="10" t="n">
         <v>1359843.142575342</v>
       </c>
-      <c r="S11" s="11" t="inlineStr"/>
-      <c r="T11" s="8" t="n">
+      <c r="S11" s="13" t="inlineStr"/>
+      <c r="T11" s="10" t="n">
         <v>6501847.893041097</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1167,7 +1214,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1181,65 +1228,65 @@
     <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Лот</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Тонн / фасовка</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Ближайший завод (ж/д)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Ближайший склад (авто)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Варианты: себестоимость с доставкой, ₽/т — расчёт</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Рекомендация</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Шаги</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>ДГХ, Московская обл.</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>400 т; не указана (уточнить)</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск (~800 км)</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Склад Люберцы, тип D (nsmgr.ru) (~70 км)</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 4 770 — Беларуськалий, Солигорск: 2430 + ж/д 800 км × 2 + перевалка 500 + авто 40 км × 6
@@ -1247,39 +1294,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 770 ₽/т → прибыль 3 144 106 ₽</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Беларуськалий цену франко-вагон + наличие МКР; 2) заказать 6 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 40 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Новосибирск, «Дзержинка»</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>400 т; МКР</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Павлодарсоль (КЗ, Таволжан) / Алтайская соледоб. (Бурсоль) (~600 км)</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 4 310 — Павлодарсоль (КЗ, Таволжан) / Алтайская соледоб. (Бурсоль): 2430 + ж/д 600 км × 2 + перевалка 500 + авто 30 км × 6
@@ -1287,39 +1334,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 310 ₽/т → прибыль 1 639 990 ₽</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Павлодарсоль (КЗ цену франко-вагон + наличие МКР; 2) заказать 6 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 30 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Волоколамск, МО</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>130 т; уточнить (Галит)</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск (~800 км)</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Склад Люберцы, тип D (nsmgr.ru) (~130 км)</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 4 650 — Беларуськалий, Солигорск: 2430 + ж/д 800 км × 2 + перевалка 500 + авто 20 км × 6
@@ -1327,39 +1374,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 650 ₽/т → прибыль 611 590 ₽</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Беларуськалий цену франко-вагон + наличие МКР; 2) заказать 2 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 20 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Абинск, Краснодарский край</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>150 т; МКР ≤1 т</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Баскунчак (Руссоль), Астраханская обл. (~900 км)</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 5 090 — Баскунчак (Руссоль), Астраханская обл.: 2430 + ж/д 900 км × 2 + перевалка 500 + авто 60 км × 6
@@ -1367,39 +1414,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 5 090 ₽/т → прибыль 310 162 ₽</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Баскунчак (Руссоль) цену франко-вагон + наличие МКР; 2) заказать 2 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 60 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Воронеж</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>461 т; МКР, помол №3</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Баскунчак (Руссоль), Астраханская обл. (~800 км)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Склад Люберцы, тип D (nsmgr.ru) (~520 км)</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 4 650 — Баскунчак (Руссоль), Астраханская обл.: 2430 + ж/д 800 км × 2 + перевалка 500 + авто 20 км × 6
@@ -1407,39 +1454,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 650 ₽/т → прибыль 480 409 ₽</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Баскунчак (Руссоль) цену франко-вагон + наличие МКР; 2) заказать 7 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 20 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Струнино, Владимирская обл.</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>150 т; МКР 0,8–1 т, Галит тип С</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск (~900 км)</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Склад Люберцы, тип D (nsmgr.ru) (~110 км)</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 4 910 — Беларуськалий, Солигорск: 2430 + ж/д 900 км × 2 + перевалка 500 + авто 30 км × 6
@@ -1447,39 +1494,39 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 4 910 ₽/т → прибыль 315 590 ₽</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Беларуськалий цену франко-вагон + наличие МКР; 2) заказать 2 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 30 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Самара (нужен опыт 24,2 млн)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>11000 т; МКР 1 т, Галит</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Илецксоль (Руссоль), Соль-Илецк (~400 км)</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша цена): 2 500 — 2 500 ₽/т с доставкой в РФ — проверить точку доставки и мин. партию
 2. Ближайший завод вагоном: 3 850 — Илецксоль (Руссоль), Соль-Илецк: 2430 + ж/д 400 км × 2 + перевалка 500 + авто 20 км × 6
@@ -1487,12 +1534,12 @@
 4. Дилер с доставкой (рынок): 8 000 — 7 000–8 500 у дилеров + доставка; верхняя граница</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном: 3 850 ₽/т → прибыль 49 542 141 ₽</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>1) Запросить у Илецксоль (Руссоль) цену франко-вагон + наличие МКР; 2) заказать 162 ваг. (~68 т/ваг.) на станцию ближе к заказчику; 3) договор с перевалкой у станции (выгрузка, хранение, погрузка МКР); 4) авто 20 км до заказчика по графику; 5) параллельно запросить КП у ближайшего склада как резерв.</t>
         </is>
@@ -1500,6 +1547,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1507,7 +1555,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1516,145 +1564,145 @@
     <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Значение / источник</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Модель прибыли</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Цена = НМЦК × (1 − 15%); прибыль = цена − себестоимость − 0,8% прочих − стоимость денег 20% годовых × 60 дн.; минус УСН 15% с прибыли.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Цена завода вагоном</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>1 990 ₽/т без НДС, ж/д норма ~70 т (esolk.ru: Павлодарсоль, Аралтуз, Уралкалий, Белкалий, Тыреть) → 2430 ₽/т с НДС 22% (для УСН НДС — расход).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Ж/д тариф</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>2 ₽/т·км с арендой полувагона [оценка; точный тариф — расчёт РЖД/оператора по станциям]. Ставки на полувагоны в 2026 выросли &gt;40%, вагонов не хватает — закладывать запас по сроку 10–20 дней.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Перевалка</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>500 ₽/т: выгрузка из вагона, временное хранение, затаривание в МКР/погрузка [оценка].</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Авто</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>6 ₽/т·км для 50–600 км [оценка]; по МО — 8–11 тыс. ₽ за машину 20–25 м³ до 60 км (perevalka-tsk.ru).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Склад РФ</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru (Люберцы): тип D 4 350–4 550 ₽/т самовывоз; Уралкалий тип A 6 500; Илецкая тип C 5 750.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Дилеры (рынок)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Аралтуз 7 000–7 800, Баскунчак/Белкалий 7 500–8 700, Уралкалий 8 000–8 500, Илецк/Тыреть 10 000 ₽/т без доставки (sknerud, vektor-e, perevalka-tsk).</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Ваша цена 2 500</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Реалистична только как цена вагоном до станции в РФ (завод КЗ ~2 000 без НДС + ж/д). Если 2 500 — до станции, добавьте перевалку и авто (+700…1 500 ₽/т).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Галит / ТУ</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Где в ТЗ «Концентрат минеральный „Галит“» (Уралкалий, ТУ) — проверить допуск эквивалента до закупки.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Фасовка МКР</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Если в ТЗ МКР, а вагон идёт навалом — затаривание на перевалке (входит в 500 ₽/т) или брать у завода сразу в МКР (+300–600 ₽/т) [оценка].</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Срок</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Подача 16–19.10; поставки обычно ноябрь–март по заявкам → держать запас на перевалке у станции ближе к заказчику.</t>
         </is>
@@ -1662,6 +1710,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1669,7 +1718,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1682,50 +1731,50 @@
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Производитель</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Продукт / фасовка</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Цена от, ₽/т</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Условия</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>esolk.ru (ЕСК)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Павлодарсоль / Аралтуз (Казахстан), Уралкалий, Белкалий, Тыреть, АСК</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Галит тип B/C, помол 2–3, навалом</t>
         </is>
@@ -1733,7 +1782,7 @@
       <c r="D2" s="15" t="n">
         <v>1990</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>без НДС, без доставки, от вагона (~70 т), станция отгрузки</t>
         </is>
@@ -1744,18 +1793,18 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Ваша цена</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Казахстан</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>МКР, НДС вкл., с доставкой в РФ</t>
         </is>
@@ -1763,29 +1812,29 @@
       <c r="D3" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>данные клиента — проверить, куда именно доставка</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru (Люберцы)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Тип D, от 40 т, россыпь/биг-бэг</t>
         </is>
@@ -1793,7 +1842,7 @@
       <c r="D4" s="15" t="n">
         <v>4350</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>самовывоз, НДС не указан</t>
         </is>
@@ -1804,18 +1853,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Тип D, до 40 т, россыпь/биг-бэг</t>
         </is>
@@ -1823,7 +1872,7 @@
       <c r="D5" s="15" t="n">
         <v>4550</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
@@ -1834,18 +1883,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>тендер Алтайский край (saby.ru)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>НМЦК 2 430 т = 13,37 млн</t>
         </is>
@@ -1853,7 +1902,7 @@
       <c r="D6" s="15" t="n">
         <v>5500</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>начальная цена заказчика, ориентир</t>
         </is>
@@ -1864,18 +1913,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Илецкая (Руссоль)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Тип C, россыпь</t>
         </is>
@@ -1883,7 +1932,7 @@
       <c r="D7" s="15" t="n">
         <v>5750</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
@@ -1894,18 +1943,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Тип C, россыпь/биг-бэг</t>
         </is>
@@ -1913,7 +1962,7 @@
       <c r="D8" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
@@ -1924,18 +1973,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Уралкалий / Белкалий</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Тип A с антислеживателем, биг-бэг</t>
         </is>
@@ -1943,7 +1992,7 @@
       <c r="D9" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
@@ -1954,18 +2003,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru (Москва)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Астрахань</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
@@ -1973,7 +2022,7 @@
       <c r="D10" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
@@ -1984,18 +2033,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Аралтуз / Индертуз / Алтайсоль (КЗ)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
@@ -2003,7 +2052,7 @@
       <c r="D11" s="15" t="n">
         <v>7000</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
@@ -2014,18 +2063,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>perevalka24.ru</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Уралкалий «Галит» марка А</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>биг-бэг 1000 кг</t>
         </is>
@@ -2033,7 +2082,7 @@
       <c r="D12" s="15" t="n">
         <v>7000</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
@@ -2044,18 +2093,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru (Москва)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>навалом</t>
         </is>
@@ -2063,7 +2112,7 @@
       <c r="D13" s="15" t="n">
         <v>7300</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>самовывоз; доставка 8–11 тыс. за машину 20–25 м³ до 60 км</t>
         </is>
@@ -2074,18 +2123,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Беларуськалий / Баскунчак</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
@@ -2093,7 +2142,7 @@
       <c r="D14" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
@@ -2104,18 +2153,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru (Москва)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь, от 2 т</t>
         </is>
@@ -2123,7 +2172,7 @@
       <c r="D15" s="15" t="n">
         <v>7800</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
@@ -2134,18 +2183,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
@@ -2153,7 +2202,7 @@
       <c r="D16" s="15" t="n">
         <v>8000</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
@@ -2164,18 +2213,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
@@ -2183,7 +2232,7 @@
       <c r="D17" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
@@ -2194,18 +2243,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
@@ -2213,7 +2262,7 @@
       <c r="D18" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
@@ -2224,18 +2273,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>навалом / биг-бэг</t>
         </is>
@@ -2243,7 +2292,7 @@
       <c r="D19" s="15" t="n">
         <v>8700</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
@@ -2254,18 +2303,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>opt6.ru</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>МКР, помол 2 тип Б</t>
         </is>
@@ -2273,7 +2322,7 @@
       <c r="D20" s="15" t="n">
         <v>9990</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
@@ -2284,18 +2333,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Тыреть / Илецксоль</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
@@ -2303,7 +2352,7 @@
       <c r="D21" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
@@ -2314,18 +2363,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Илецкая</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
@@ -2333,7 +2382,7 @@
       <c r="D22" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
@@ -2344,18 +2393,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Руссоль-центр</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Руссоль</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>мешки/МКР, от 10 т</t>
         </is>
@@ -2363,7 +2412,7 @@
       <c r="D23" s="15" t="n">
         <v>11300</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>опт, по данным выдачи поиска (сайт 403)</t>
         </is>
@@ -2400,5 +2449,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>